--- a/app/config/tables/sentinela/forms/resultado/resultado.xlsx
+++ b/app/config/tables/sentinela/forms/resultado/resultado.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\resultado\forms\ronda\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11877B6-B8AB-412F-83D3-87A27905D849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40843006-33EF-4A6A-BFA9-CD37549E1E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="124">
   <si>
     <t>type</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>DOB_idade</t>
+  </si>
+  <si>
+    <t>sentinela</t>
   </si>
 </sst>
 </file>
@@ -590,11 +593,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="14">
@@ -1065,7 +1068,7 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1572,21 +1575,21 @@
       <c r="H45" s="15"/>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
       <c r="H46" s="15"/>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
-      <c r="G47" s="18"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
       <c r="H47" s="15"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -2454,7 +2457,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>45</v>
       </c>
       <c r="B13" t="s">

--- a/app/config/tables/sentinela/forms/resultado/resultado.xlsx
+++ b/app/config/tables/sentinela/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40843006-33EF-4A6A-BFA9-CD37549E1E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D6477D-9AF9-4F64-A96F-EDDD8CE8A007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
   <si>
     <t>type</t>
   </si>
@@ -182,9 +182,6 @@
     <t>branch_label</t>
   </si>
   <si>
-    <t>sticker</t>
-  </si>
-  <si>
     <t>begin screen</t>
   </si>
   <si>
@@ -194,15 +191,6 @@
     <t>note</t>
   </si>
   <si>
-    <t>ending</t>
-  </si>
-  <si>
-    <t>survey_complete</t>
-  </si>
-  <si>
-    <t>A exibição agora está completa, por favor, vá para a próxima página para finalizar suas respostas.</t>
-  </si>
-  <si>
     <t>adate</t>
   </si>
   <si>
@@ -221,15 +209,6 @@
     <t>data('tdr')=='1'</t>
   </si>
   <si>
-    <t>if // error_qr</t>
-  </si>
-  <si>
-    <t>erro_qr</t>
-  </si>
-  <si>
-    <t>end if // error_qr</t>
-  </si>
-  <si>
     <t>comentario_1</t>
   </si>
   <si>
@@ -242,15 +221,6 @@
     <t>Está a fazer entrevista com: {{data.nome}} e ID: {{data.id_paciente}}</t>
   </si>
   <si>
-    <t>Introduza o numero se serie do cartao</t>
-  </si>
-  <si>
-    <t>data('sticker') != data('id_paciente')</t>
-  </si>
-  <si>
-    <t>o Codigo da Pessoa ({{data.id_paciente}} não corresponde ao codigo introduzido  ({{data.sticker}}).</t>
-  </si>
-  <si>
     <t>nome_casa</t>
   </si>
   <si>
@@ -296,9 +266,6 @@
     <t>adate.display(calculates.hoje())</t>
   </si>
   <si>
-    <t>""+"----Ronda - "+ data('n_ronda') + "Dia-"+ data('dia')</t>
-  </si>
-  <si>
     <t>resultado</t>
   </si>
   <si>
@@ -405,13 +372,22 @@
   </si>
   <si>
     <t>sentinela</t>
+  </si>
+  <si>
+    <t>cs</t>
+  </si>
+  <si>
+    <t>comentario_2</t>
+  </si>
+  <si>
+    <t>id_formssentinela</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -465,31 +441,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="4">
@@ -550,7 +513,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -571,19 +534,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -593,7 +543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1044,7 +994,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1060,7 +1010,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1068,15 +1018,15 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1108,18 +1058,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1080,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y54"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -1162,7 +1112,7 @@
       <c r="C1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -1196,10 +1146,10 @@
         <v>26</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="Q1" t="s">
         <v>27</v>
@@ -1252,418 +1202,306 @@
       <c r="X2"/>
       <c r="Y2"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B3" s="17" t="s">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="O7"/>
+      <c r="P7"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8"/>
+      <c r="P8"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O9"/>
+      <c r="P9"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="6"/>
-      <c r="I3"/>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
-      <c r="N3"/>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3"/>
-      <c r="R3"/>
-      <c r="S3"/>
-      <c r="T3"/>
-      <c r="U3"/>
-      <c r="V3"/>
-      <c r="W3"/>
-      <c r="X3"/>
-      <c r="Y3"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2" t="s">
+      <c r="E14" s="10"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="K5" s="11"/>
-    </row>
-    <row r="6" spans="1:25" s="10" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="K6" s="11"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-    </row>
-    <row r="7" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="14"/>
-    </row>
-    <row r="8" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="K8" s="11"/>
-    </row>
-    <row r="9" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="11"/>
-    </row>
-    <row r="10" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K10" s="11"/>
-    </row>
-    <row r="11" spans="1:25" s="10" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="D11" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="K11" s="11"/>
-    </row>
-    <row r="12" spans="1:25" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="K12" s="11"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="K14" s="4"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="O15"/>
-      <c r="P15"/>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="O16"/>
-      <c r="P16"/>
-    </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17"/>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="O18"/>
-      <c r="P18"/>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D20" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="E25" s="15"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="E26" s="15"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="K30" s="4"/>
-    </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="K31" s="4"/>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-    </row>
-    <row r="36" spans="1:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="K38" s="4"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="D40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="D41" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="W41" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="15"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="15"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15"/>
+      <c r="G16" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E17" s="10"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="K21" s="4"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="K22" s="4"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K29" s="4"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="10"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="E46:E47"/>
-    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -1722,7 +1560,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1733,7 +1571,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1774,101 +1612,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2353,7 +2191,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -2378,18 +2216,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2397,7 +2235,7 @@
         <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2413,15 +2251,15 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2429,7 +2267,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2437,7 +2275,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2445,23 +2283,23 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2469,15 +2307,15 @@
         <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2485,7 +2323,7 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2493,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2501,7 +2339,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2509,7 +2347,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2517,31 +2355,63 @@
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2466,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
         <v>45</v>
@@ -2605,7 +2475,7 @@
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/app/config/tables/sentinela/forms/resultado/resultado.xlsx
+++ b/app/config/tables/sentinela/forms/resultado/resultado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\sentinela\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D6477D-9AF9-4F64-A96F-EDDD8CE8A007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0CAF54-7D1E-48F7-BD32-21C0343CBAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="117">
   <si>
     <t>type</t>
   </si>
@@ -377,17 +377,20 @@
     <t>cs</t>
   </si>
   <si>
-    <t>comentario_2</t>
-  </si>
-  <si>
     <t>id_formssentinela</t>
+  </si>
+  <si>
+    <t>select_one_dropdown</t>
+  </si>
+  <si>
+    <t>comentario</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -439,12 +442,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -513,7 +510,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -542,9 +539,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1239,6 +1233,9 @@
       </c>
       <c r="H6"/>
       <c r="I6"/>
+      <c r="L6" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="O6"/>
       <c r="P6"/>
     </row>
@@ -1265,6 +1262,9 @@
       <c r="G8" s="2" t="s">
         <v>95</v>
       </c>
+      <c r="L8" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="O8"/>
       <c r="P8"/>
     </row>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="2" t="s">
@@ -1413,21 +1413,21 @@
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
@@ -2191,7 +2191,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.125" customWidth="1"/>
@@ -2208,74 +2208,74 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2283,63 +2283,63 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2347,36 +2347,47 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" t="s">
-        <v>115</v>
+      <c r="B25" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>97</v>
@@ -2407,12 +2418,28 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
